--- a/TEVA.xlsx
+++ b/TEVA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F1FA71-2138-4A45-B57A-9A38AFCD181F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3CB68A-F4CB-4937-AF60-28494E6A480D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26400" yWindow="1470" windowWidth="25080" windowHeight="18540" xr2:uid="{D2213452-9D24-42F2-9207-6C5DFE94D9E3}"/>
+    <workbookView xWindow="13160" yWindow="4120" windowWidth="19050" windowHeight="16100" xr2:uid="{D2213452-9D24-42F2-9207-6C5DFE94D9E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
     <t>CEO: Richard Francis replaces Kare Schultz</t>
   </si>
   <si>
-    <t>Q224</t>
+    <t>Q226</t>
   </si>
 </sst>
 </file>
@@ -439,68 +439,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F66CF8-4FB6-4568-8AB0-FDB25D3CA399}">
   <dimension ref="L2:N9"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="12:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="12:14" x14ac:dyDescent="0.25">
       <c r="L2" t="s">
         <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>21.42</v>
-      </c>
-    </row>
-    <row r="3" spans="12:14" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="12:14" x14ac:dyDescent="0.25">
       <c r="L3" t="s">
         <v>1</v>
       </c>
       <c r="M3" s="3">
-        <v>1133</v>
+        <v>1191</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="12:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="12:14" x14ac:dyDescent="0.25">
       <c r="L4" t="s">
         <v>2</v>
       </c>
       <c r="M4" s="3">
         <f>+M2*M3</f>
-        <v>24268.86</v>
-      </c>
-    </row>
-    <row r="5" spans="12:14" x14ac:dyDescent="0.2">
+        <v>40494</v>
+      </c>
+    </row>
+    <row r="5" spans="12:14" x14ac:dyDescent="0.25">
       <c r="L5" t="s">
         <v>3</v>
       </c>
       <c r="M5" s="3">
-        <v>2258</v>
+        <v>3655</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="12:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="12:14" x14ac:dyDescent="0.25">
       <c r="L6" t="s">
         <v>4</v>
       </c>
       <c r="M6" s="3">
-        <v>18640</v>
+        <v>16593</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="12:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="12:14" x14ac:dyDescent="0.25">
       <c r="L7" t="s">
         <v>5</v>
       </c>
       <c r="M7" s="3">
         <f>+M4-M5+M6</f>
-        <v>40650.86</v>
-      </c>
-    </row>
-    <row r="9" spans="12:14" x14ac:dyDescent="0.2">
+        <v>53432</v>
+      </c>
+    </row>
+    <row r="9" spans="12:14" x14ac:dyDescent="0.25">
       <c r="L9" t="s">
         <v>6</v>
       </c>
@@ -513,7 +513,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69CA9D26-9673-45DF-B032-216B3A99BA0B}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
